--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137132014</v>
+        <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>92355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Moren, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707972</v>
+        <v>708014</v>
       </c>
       <c r="R2" t="n">
-        <v>7211525</v>
+        <v>7211568</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +755,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:14</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,55 +771,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132014</t>
+          <t>https://artportalen.se/Sighting/137149199</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137132003</v>
+        <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>83354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708060</v>
+        <v>707972</v>
       </c>
       <c r="R3" t="n">
-        <v>7211672</v>
+        <v>7211525</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,54 +901,61 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132003</t>
+          <t>https://artportalen.se/Sighting/137132014</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137132004</v>
+        <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Moren, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>708056</v>
+        <v>708021</v>
       </c>
       <c r="R4" t="n">
-        <v>7211675</v>
+        <v>7211664</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,54 +982,45 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132004</t>
+          <t>https://artportalen.se/Sighting/137149311</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137132006</v>
+        <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708048</v>
+        <v>708060</v>
       </c>
       <c r="R5" t="n">
-        <v>7211651</v>
+        <v>7211672</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,16 +1123,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132006</t>
+          <t>https://artportalen.se/Sighting/137132003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137132009</v>
+        <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708053</v>
+        <v>708056</v>
       </c>
       <c r="R6" t="n">
-        <v>7211534</v>
+        <v>7211675</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,62 +1235,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132009</t>
+          <t>https://artportalen.se/Sighting/137132004</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137132002</v>
+        <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valpselbäcken, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708060</v>
+        <v>708048</v>
       </c>
       <c r="R7" t="n">
-        <v>7211672</v>
+        <v>7211651</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,12 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,62 +1347,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132002</t>
+          <t>https://artportalen.se/Sighting/137132006</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137132008</v>
+        <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valpselbäcken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708125</v>
+        <v>708053</v>
       </c>
       <c r="R8" t="n">
-        <v>7211555</v>
+        <v>7211534</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,12 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,59 +1459,58 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132008</t>
+          <t>https://artportalen.se/Sighting/137132009</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137132007</v>
+        <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Moren, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708044</v>
+        <v>708161</v>
       </c>
       <c r="R9" t="n">
-        <v>7211579</v>
+        <v>7211713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,105 +1540,90 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132007</t>
+          <t>https://artportalen.se/Sighting/137148823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137132010</v>
+        <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Moren, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708037</v>
+        <v>708171</v>
       </c>
       <c r="R10" t="n">
-        <v>7211556</v>
+        <v>7211643</v>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,105 +1650,90 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosök genom barksprätt</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132010</t>
+          <t>https://artportalen.se/Sighting/137148877</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137132011</v>
+        <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Moren, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708024</v>
+        <v>708136</v>
       </c>
       <c r="R11" t="n">
-        <v>7211585</v>
+        <v>7211619</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,50 +1760,1106 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosök genom barksprätt</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137148907</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137148935</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Moren, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>708117</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7211547</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148935</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137149242</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Moren, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>708006</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7211537</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149242</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137149303</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Moren, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>707981</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7211620</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149303</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137132002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>708060</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7211672</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132002</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137132008</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>708125</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7211555</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132008</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137132007</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>708044</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7211579</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137132010</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>708037</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7211556</v>
+      </c>
+      <c r="S18" t="n">
+        <v>27</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök genom barksprätt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132010</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137132011</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>708024</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7211585</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosök genom barksprätt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137132011</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137148852</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Moren, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>708164</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7211707</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137148852</t>
         </is>
       </c>
     </row>
@@ -1875,6 +2875,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92355</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Tommy Boström, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,56 +2125,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137132002</v>
+        <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Bäverhult östra, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708060</v>
+        <v>708166</v>
       </c>
       <c r="R15" t="n">
-        <v>7211672</v>
+        <v>7211649</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2203,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2213,12 +2205,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,73 +2220,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132002</t>
+          <t>https://artportalen.se/Sighting/137234276</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137132008</v>
+        <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Bäverhult östra, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708125</v>
+        <v>708150</v>
       </c>
       <c r="R16" t="n">
-        <v>7211555</v>
+        <v>7211603</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,12 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,73 +2332,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132008</t>
+          <t>https://artportalen.se/Sighting/137234277</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137132007</v>
+        <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valpselbäcken, Vb</t>
+          <t>Bäverhult östra, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708044</v>
+        <v>708109</v>
       </c>
       <c r="R17" t="n">
-        <v>7211579</v>
+        <v>7211537</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,7 +2419,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,12 +2429,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,44 +2444,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132007</t>
+          <t>https://artportalen.se/Sighting/137234279</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137132010</v>
+        <v>137132002</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2543,13 +2504,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708037</v>
+        <v>708060</v>
       </c>
       <c r="R18" t="n">
-        <v>7211556</v>
+        <v>7211672</v>
       </c>
       <c r="S18" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2578,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,12 +2549,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosök genom barksprätt</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,33 +2580,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132010</t>
+          <t>https://artportalen.se/Sighting/137132002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137132011</v>
+        <v>137132008</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2658,7 +2619,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2668,13 +2629,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708024</v>
+        <v>708125</v>
       </c>
       <c r="R19" t="n">
-        <v>7211585</v>
+        <v>7211555</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födosök genom barksprätt</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,16 +2705,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132011</t>
+          <t>https://artportalen.se/Sighting/137132008</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137148852</v>
+        <v>137132007</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,14 +2750,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Moren, Vb</t>
+          <t>Valpselbäcken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708164</v>
+        <v>708044</v>
       </c>
       <c r="R20" t="n">
-        <v>7211707</v>
+        <v>7211579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,14 +2787,24 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,16 +2819,381 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132007</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137132010</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>708037</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7211556</v>
+      </c>
+      <c r="S21" t="n">
+        <v>27</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosök genom barksprätt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132010</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137132011</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Valpselbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>708024</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7211585</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosök genom barksprätt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132011</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137148852</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Moren, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>708164</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7211707</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137148852</t>
         </is>
@@ -2884,6 +3220,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström, Patrik Nygren</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>137132002</v>
       </c>
       <c r="B18" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137132008</v>
       </c>
       <c r="B19" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137132007</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>137132010</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>137132011</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137148852</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -2492,11 +2492,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2617,11 +2613,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2742,11 +2734,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2867,11 +2855,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2992,11 +2976,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3117,11 +3097,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92375</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>137132002</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137132008</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137132007</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137132010</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>137132011</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>137148852</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>137132002</v>
       </c>
       <c r="B18" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137132008</v>
       </c>
       <c r="B19" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137132007</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137132010</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>137132011</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>137148852</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>137132002</v>
       </c>
       <c r="B18" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137132008</v>
       </c>
       <c r="B19" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137132007</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137132010</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>137132011</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>137148852</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Tommy Boström, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström, Patrik Nygren</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92409</v>
+        <v>92412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37302-2026 artfynd.xlsx
+++ b/artfynd/A 37302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149199</v>
       </c>
       <c r="B2" t="n">
-        <v>92412</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137132014</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137149311</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137132003</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137132004</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137132006</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137132009</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137148823</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137148877</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137148907</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137148935</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137149242</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137149303</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137234276</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137234277</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137234279</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>137132002</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137132008</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137132007</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137132010</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>137132011</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>137148852</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
